--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:08:00+00:00</t>
+    <t>2025-05-12T08:18:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:18:40+00:00</t>
+    <t>2025-05-12T08:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:26:30+00:00</t>
+    <t>2025-05-12T09:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:15:35+00:00</t>
+    <t>2025-05-12T09:44:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:44:35+00:00</t>
+    <t>2025-05-12T09:48:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T09:48:13+00:00</t>
+    <t>2025-05-12T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T10:07:46+00:00</t>
+    <t>2025-05-12T12:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:08:59+00:00</t>
+    <t>2025-05-12T12:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:21:25+00:00</t>
+    <t>2025-05-12T12:41:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T12:41:16+00:00</t>
+    <t>2025-05-12T13:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T13:04:33+00:00</t>
+    <t>2025-05-12T14:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T14:29:06+00:00</t>
+    <t>2025-05-12T14:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T14:37:35+00:00</t>
+    <t>2025-05-12T15:04:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T15:04:22+00:00</t>
+    <t>2025-05-13T10:20:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:20:58+00:00</t>
+    <t>2025-05-20T13:44:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:44:07+00:00</t>
+    <t>2025-05-20T13:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:46:53+00:00</t>
+    <t>2025-05-20T13:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:54:28+00:00</t>
+    <t>2025-05-20T13:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:56:00+00:00</t>
+    <t>2025-05-23T16:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T16:42:05+00:00</t>
+    <t>2025-05-23T16:51:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T16:51:26+00:00</t>
+    <t>2025-05-24T07:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-24T07:13:38+00:00</t>
+    <t>2025-05-26T07:36:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
+++ b/nr-add-examples/ig/ValueSet-fr-core-vs-identity-reliability.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T07:36:52+00:00</t>
+    <t>2025-05-28T11:10:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
